--- a/measurements/28/Filled_2D_sections/axial/week28_axial_Batch_Allmarks.xlsx
+++ b/measurements/28/Filled_2D_sections/axial/week28_axial_Batch_Allmarks.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O24"/>
+  <dimension ref="A1:AD27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -487,12 +487,87 @@
           <t>mean_depth_mm</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Primary_count</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Primary_v1_mm</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Primary_v2_mm</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Secondary_count</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>Secondary_v1_mm</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>Secondary_v2_mm</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>Secondary_v3_mm</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>Tertiary_count</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>Tertiary_v1_mm</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>Tertiary_v2_mm</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>Tertiary_v3_mm</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>Tertiary_min_mm</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>Tertiary_max_mm</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Tertiary_mean_mm</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>Unclassified_count</t>
+        </is>
+      </c>
+      <c r="AC1" t="inlineStr">
         <is>
           <t>Metric</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>Mean</t>
         </is>
@@ -506,17 +581,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>axial</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>7.462522308149911</v>
+        <v>2844.557823129252</v>
       </c>
       <c r="D2" t="n">
-        <v>16.34139106331802</v>
+        <v>319.0462064743042</v>
       </c>
       <c r="E2" t="n">
-        <v>11.52480020174166</v>
+        <v>225.0080039387657</v>
       </c>
       <c r="F2" t="n">
         <v>1.41793269967912</v>
@@ -525,24 +600,51 @@
         <v>0.3511700424662357</v>
       </c>
       <c r="H2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I2" t="n">
-        <v>1.512766768292683</v>
+        <v>1.225818452380952</v>
       </c>
       <c r="J2" t="n">
-        <v>1.512766768292683</v>
+        <v>29.53497023809524</v>
       </c>
       <c r="K2" t="n">
-        <v>1.512766768292683</v>
-      </c>
-      <c r="N2" t="inlineStr">
+        <v>9.83407738095238</v>
+      </c>
+      <c r="L2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M2" t="n">
+        <v>29.53497023809524</v>
+      </c>
+      <c r="O2" t="n">
+        <v>3</v>
+      </c>
+      <c r="P2" t="n">
+        <v>7.366071428571428</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>6.690848214285714</v>
+      </c>
+      <c r="R2" t="n">
+        <v>4.352678571428571</v>
+      </c>
+      <c r="S2" t="n">
+        <v>1</v>
+      </c>
+      <c r="T2" t="n">
+        <v>1.225818452380952</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC2" t="inlineStr">
         <is>
           <t>area</t>
         </is>
       </c>
-      <c r="O2" s="2" t="n">
-        <v>7.473899464604402</v>
+      <c r="AD2" s="2" t="n">
+        <v>2848.894557823129</v>
       </c>
     </row>
     <row r="3">
@@ -553,43 +655,67 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>axial</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>7.478286734086853</v>
+        <v>2850.566893424036</v>
       </c>
       <c r="D3" t="n">
-        <v>16.29015928652229</v>
+        <v>318.0459670225779</v>
       </c>
       <c r="E3" t="n">
-        <v>11.70563463757678</v>
+        <v>228.5385810193561</v>
       </c>
       <c r="F3" t="n">
-        <v>1.391651097175759</v>
+        <v>1.391651097175758</v>
       </c>
       <c r="G3" t="n">
-        <v>0.3541288549614018</v>
+        <v>0.354128854961402</v>
       </c>
       <c r="H3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I3" t="n">
-        <v>1.545255335365854</v>
+        <v>4.797247023809524</v>
       </c>
       <c r="J3" t="n">
-        <v>1.545255335365854</v>
+        <v>30.16927083333333</v>
       </c>
       <c r="K3" t="n">
-        <v>1.545255335365854</v>
-      </c>
-      <c r="N3" t="inlineStr">
+        <v>12.26981026785714</v>
+      </c>
+      <c r="L3" t="n">
+        <v>1</v>
+      </c>
+      <c r="M3" t="n">
+        <v>30.16927083333333</v>
+      </c>
+      <c r="O3" t="n">
+        <v>3</v>
+      </c>
+      <c r="P3" t="n">
+        <v>7.418154761904762</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>6.694568452380952</v>
+      </c>
+      <c r="R3" t="n">
+        <v>4.797247023809524</v>
+      </c>
+      <c r="S3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC3" t="inlineStr">
         <is>
           <t>perimeter</t>
         </is>
       </c>
-      <c r="O3" s="2" t="n">
-        <v>14.25942591806738</v>
+      <c r="AD3" s="2" t="n">
+        <v>278.3983155432201</v>
       </c>
     </row>
     <row r="4">
@@ -600,43 +726,67 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>axial</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>7.494348602022606</v>
+        <v>2856.689342403628</v>
       </c>
       <c r="D4" t="n">
-        <v>16.41629519695189</v>
+        <v>320.5086205119178</v>
       </c>
       <c r="E4" t="n">
-        <v>11.79727754941801</v>
+        <v>230.3277997743516</v>
       </c>
       <c r="F4" t="n">
         <v>1.391532506392693</v>
       </c>
       <c r="G4" t="n">
-        <v>0.3494567621351347</v>
+        <v>0.3494567621351348</v>
       </c>
       <c r="H4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I4" t="n">
-        <v>1.506192835365854</v>
+        <v>4.56845238095238</v>
       </c>
       <c r="J4" t="n">
-        <v>1.506192835365854</v>
+        <v>29.40662202380952</v>
       </c>
       <c r="K4" t="n">
-        <v>1.506192835365854</v>
-      </c>
-      <c r="N4" t="inlineStr">
+        <v>12.01636904761905</v>
+      </c>
+      <c r="L4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M4" t="n">
+        <v>29.40662202380952</v>
+      </c>
+      <c r="O4" t="n">
+        <v>3</v>
+      </c>
+      <c r="P4" t="n">
+        <v>7.287946428571428</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>6.802455357142857</v>
+      </c>
+      <c r="R4" t="n">
+        <v>4.56845238095238</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC4" t="inlineStr">
         <is>
           <t>perimeter_convex</t>
         </is>
       </c>
-      <c r="O4" s="2" t="n">
-        <v>11.56228556124175</v>
+      <c r="AD4" s="2" t="n">
+        <v>225.7398609575771</v>
       </c>
     </row>
     <row r="5">
@@ -647,17 +797,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>axial</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>7.539262343842951</v>
+        <v>2873.809523809523</v>
       </c>
       <c r="D5" t="n">
-        <v>16.51630750516566</v>
+        <v>322.46124176752</v>
       </c>
       <c r="E5" t="n">
-        <v>11.86626357857774</v>
+        <v>231.6746698674701</v>
       </c>
       <c r="F5" t="n">
         <v>1.39187094537346</v>
@@ -666,23 +816,47 @@
         <v>0.3473064105601356</v>
       </c>
       <c r="H5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I5" t="n">
-        <v>1.450171493902439</v>
+        <v>4.877232142857142</v>
       </c>
       <c r="J5" t="n">
-        <v>1.450171493902439</v>
+        <v>28.31287202380952</v>
       </c>
       <c r="K5" t="n">
-        <v>1.450171493902439</v>
-      </c>
-      <c r="N5" t="inlineStr">
+        <v>11.79501488095238</v>
+      </c>
+      <c r="L5" t="n">
+        <v>1</v>
+      </c>
+      <c r="M5" t="n">
+        <v>28.31287202380952</v>
+      </c>
+      <c r="O5" t="n">
+        <v>3</v>
+      </c>
+      <c r="P5" t="n">
+        <v>7.176339285714286</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>6.813616071428571</v>
+      </c>
+      <c r="R5" t="n">
+        <v>4.877232142857142</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC5" t="inlineStr">
         <is>
           <t>LGI</t>
         </is>
       </c>
-      <c r="O5" s="2" t="n">
+      <c r="AD5" s="2" t="n">
         <v>1.232463057758511</v>
       </c>
     </row>
@@ -694,42 +868,66 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>axial</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>7.688578227245688</v>
+        <v>2930.725623582766</v>
       </c>
       <c r="D6" t="n">
-        <v>15.18046477364331</v>
+        <v>296.3805027235122</v>
       </c>
       <c r="E6" t="n">
-        <v>11.82585249586803</v>
+        <v>230.8856915859949</v>
       </c>
       <c r="F6" t="n">
-        <v>1.283667691521384</v>
+        <v>1.283667691521383</v>
       </c>
       <c r="G6" t="n">
         <v>0.4192622539139519</v>
       </c>
       <c r="H6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I6" t="n">
-        <v>1.16968368902439</v>
+        <v>5.014880952380952</v>
       </c>
       <c r="J6" t="n">
-        <v>1.16968368902439</v>
+        <v>22.83668154761905</v>
       </c>
       <c r="K6" t="n">
-        <v>1.16968368902439</v>
-      </c>
-      <c r="N6" t="inlineStr">
+        <v>10.44363839285714</v>
+      </c>
+      <c r="L6" t="n">
+        <v>1</v>
+      </c>
+      <c r="M6" t="n">
+        <v>22.83668154761905</v>
+      </c>
+      <c r="O6" t="n">
+        <v>3</v>
+      </c>
+      <c r="P6" t="n">
+        <v>6.969866071428571</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>6.953125</v>
+      </c>
+      <c r="R6" t="n">
+        <v>5.014880952380952</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC6" t="inlineStr">
         <is>
           <t>Compactness</t>
         </is>
       </c>
-      <c r="O6" s="2" t="n">
+      <c r="AD6" s="2" t="n">
         <v>0.4731195902887243</v>
       </c>
     </row>
@@ -741,43 +939,70 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>axial</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>7.635336109458656</v>
+        <v>2910.430839002267</v>
       </c>
       <c r="D7" t="n">
-        <v>14.74042501391434</v>
+        <v>287.7892502716609</v>
       </c>
       <c r="E7" t="n">
-        <v>11.8115650182817</v>
+        <v>230.6067455950237</v>
       </c>
       <c r="F7" t="n">
         <v>1.247965446670226</v>
       </c>
       <c r="G7" t="n">
-        <v>0.4415887614635581</v>
+        <v>0.4415887614635582</v>
       </c>
       <c r="H7" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I7" t="n">
-        <v>1.077553353658537</v>
+        <v>1.214657738095238</v>
       </c>
       <c r="J7" t="n">
-        <v>1.077553353658537</v>
+        <v>21.03794642857143</v>
       </c>
       <c r="K7" t="n">
-        <v>1.077553353658537</v>
-      </c>
-      <c r="N7" t="inlineStr">
+        <v>8.350446428571429</v>
+      </c>
+      <c r="L7" t="n">
+        <v>1</v>
+      </c>
+      <c r="M7" t="n">
+        <v>21.03794642857143</v>
+      </c>
+      <c r="O7" t="n">
+        <v>3</v>
+      </c>
+      <c r="P7" t="n">
+        <v>7.520461309523809</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>6.9140625</v>
+      </c>
+      <c r="R7" t="n">
+        <v>5.065104166666666</v>
+      </c>
+      <c r="S7" t="n">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>1.214657738095238</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC7" t="inlineStr">
         <is>
           <t>Sulci_count</t>
         </is>
       </c>
-      <c r="O7" s="2" t="n">
-        <v>1.1</v>
+      <c r="AD7" s="2" t="n">
+        <v>5.15</v>
       </c>
     </row>
     <row r="8">
@@ -788,43 +1013,70 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>axial</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>7.560975609756098</v>
+        <v>2882.086167800453</v>
       </c>
       <c r="D8" t="n">
-        <v>14.66306957965944</v>
+        <v>286.2789775076366</v>
       </c>
       <c r="E8" t="n">
-        <v>12.03872863548558</v>
+        <v>235.0418447880518</v>
       </c>
       <c r="F8" t="n">
         <v>1.217991535787118</v>
       </c>
       <c r="G8" t="n">
-        <v>0.4419141525665098</v>
+        <v>0.44191415256651</v>
       </c>
       <c r="H8" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I8" t="n">
-        <v>1.026772103658537</v>
+        <v>1.222098214285714</v>
       </c>
       <c r="J8" t="n">
-        <v>1.026772103658537</v>
+        <v>20.04650297619047</v>
       </c>
       <c r="K8" t="n">
-        <v>1.026772103658537</v>
-      </c>
-      <c r="N8" t="inlineStr">
+        <v>8.402157738095237</v>
+      </c>
+      <c r="L8" t="n">
+        <v>1</v>
+      </c>
+      <c r="M8" t="n">
+        <v>20.04650297619047</v>
+      </c>
+      <c r="O8" t="n">
+        <v>3</v>
+      </c>
+      <c r="P8" t="n">
+        <v>8.433779761904761</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>6.9921875</v>
+      </c>
+      <c r="R8" t="n">
+        <v>5.316220238095238</v>
+      </c>
+      <c r="S8" t="n">
+        <v>1</v>
+      </c>
+      <c r="T8" t="n">
+        <v>1.222098214285714</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC8" t="inlineStr">
         <is>
           <t>min_depth_mm</t>
         </is>
       </c>
-      <c r="O8" s="2" t="n">
-        <v>1.03530868902439</v>
+      <c r="AD8" s="2" t="n">
+        <v>2.542782738095238</v>
       </c>
     </row>
     <row r="9">
@@ -835,17 +1087,17 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>axial</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>7.489886972040453</v>
+        <v>2854.988662131519</v>
       </c>
       <c r="D9" t="n">
-        <v>14.41324910594196</v>
+        <v>281.4015301636287</v>
       </c>
       <c r="E9" t="n">
-        <v>12.15649516989545</v>
+        <v>237.3410961741493</v>
       </c>
       <c r="F9" t="n">
         <v>1.185641823939121</v>
@@ -854,24 +1106,51 @@
         <v>0.4530658649284184</v>
       </c>
       <c r="H9" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I9" t="n">
-        <v>0.978563262195122</v>
+        <v>1.322544642857143</v>
       </c>
       <c r="J9" t="n">
-        <v>0.978563262195122</v>
+        <v>19.10528273809524</v>
       </c>
       <c r="K9" t="n">
-        <v>0.978563262195122</v>
-      </c>
-      <c r="N9" t="inlineStr">
+        <v>8.254092261904763</v>
+      </c>
+      <c r="L9" t="n">
+        <v>1</v>
+      </c>
+      <c r="M9" t="n">
+        <v>19.10528273809524</v>
+      </c>
+      <c r="O9" t="n">
+        <v>3</v>
+      </c>
+      <c r="P9" t="n">
+        <v>8.493303571428571</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>7.020089285714286</v>
+      </c>
+      <c r="R9" t="n">
+        <v>5.329241071428571</v>
+      </c>
+      <c r="S9" t="n">
+        <v>1</v>
+      </c>
+      <c r="T9" t="n">
+        <v>1.322544642857143</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC9" t="inlineStr">
         <is>
           <t>max_depth_mm</t>
         </is>
       </c>
-      <c r="O9" s="2" t="n">
-        <v>1.042902057926829</v>
+      <c r="AD9" s="2" t="n">
+        <v>20.36142113095238</v>
       </c>
     </row>
     <row r="10">
@@ -882,43 +1161,70 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>axial</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>7.387566924449732</v>
+        <v>2815.986394557823</v>
       </c>
       <c r="D10" t="n">
-        <v>13.81604709567093</v>
+        <v>269.7418718678611</v>
       </c>
       <c r="E10" t="n">
-        <v>12.27426166650726</v>
+        <v>239.6403468222845</v>
       </c>
       <c r="F10" t="n">
         <v>1.125611256387889</v>
       </c>
       <c r="G10" t="n">
-        <v>0.4863441342857455</v>
+        <v>0.4863441342857457</v>
       </c>
       <c r="H10" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I10" t="n">
-        <v>0.7082698170731707</v>
+        <v>1.086309523809524</v>
       </c>
       <c r="J10" t="n">
-        <v>0.7082698170731707</v>
+        <v>13.828125</v>
       </c>
       <c r="K10" t="n">
-        <v>0.7082698170731707</v>
-      </c>
-      <c r="N10" t="inlineStr">
+        <v>7.497767857142859</v>
+      </c>
+      <c r="L10" t="n">
+        <v>1</v>
+      </c>
+      <c r="M10" t="n">
+        <v>13.828125</v>
+      </c>
+      <c r="O10" t="n">
+        <v>3</v>
+      </c>
+      <c r="P10" t="n">
+        <v>9.680059523809524</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>7.412574404761904</v>
+      </c>
+      <c r="R10" t="n">
+        <v>5.481770833333333</v>
+      </c>
+      <c r="S10" t="n">
+        <v>1</v>
+      </c>
+      <c r="T10" t="n">
+        <v>1.086309523809524</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC10" t="inlineStr">
         <is>
           <t>mean_depth_mm</t>
         </is>
       </c>
-      <c r="O10" s="2" t="n">
-        <v>1.03910537347561</v>
+      <c r="AD10" s="2" t="n">
+        <v>8.006554483772675</v>
       </c>
     </row>
     <row r="11">
@@ -929,17 +1235,17 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>axial</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>7.249256395002975</v>
+        <v>2763.265306122449</v>
       </c>
       <c r="D11" t="n">
-        <v>13.83380128697651</v>
+        <v>270.0885013171605</v>
       </c>
       <c r="E11" t="n">
-        <v>12.14812574735502</v>
+        <v>237.1776931626456</v>
       </c>
       <c r="F11" t="n">
         <v>1.138760132606341</v>
@@ -948,16 +1254,48 @@
         <v>0.4760145835204307</v>
       </c>
       <c r="H11" t="n">
+        <v>4</v>
+      </c>
+      <c r="I11" t="n">
+        <v>4.761904761904762</v>
+      </c>
+      <c r="J11" t="n">
+        <v>12.36793154761905</v>
+      </c>
+      <c r="K11" t="n">
+        <v>9.161551339285714</v>
+      </c>
+      <c r="L11" t="n">
         <v>2</v>
       </c>
-      <c r="I11" t="n">
-        <v>0.5533536585365854</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0.6334794207317074</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0.5934165396341464</v>
+      <c r="M11" t="n">
+        <v>12.36793154761905</v>
+      </c>
+      <c r="N11" t="n">
+        <v>10.80357142857143</v>
+      </c>
+      <c r="O11" t="n">
+        <v>2</v>
+      </c>
+      <c r="P11" t="n">
+        <v>8.712797619047619</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>4.761904761904762</v>
+      </c>
+      <c r="S11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Primary_count</t>
+        </is>
+      </c>
+      <c r="AD11" s="2" t="n">
+        <v>1.1</v>
       </c>
     </row>
     <row r="12">
@@ -968,35 +1306,67 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>axial</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>7.175490779298038</v>
+        <v>2735.147392290249</v>
       </c>
       <c r="D12" t="n">
-        <v>14.1383203326202</v>
+        <v>276.0338731606801</v>
       </c>
       <c r="E12" t="n">
-        <v>11.88646910830242</v>
+        <v>232.0691587811424</v>
       </c>
       <c r="F12" t="n">
         <v>1.189446605531067</v>
       </c>
       <c r="G12" t="n">
-        <v>0.451092742775112</v>
+        <v>0.4510927427751119</v>
       </c>
       <c r="H12" t="n">
+        <v>4</v>
+      </c>
+      <c r="I12" t="n">
+        <v>5.063244047619047</v>
+      </c>
+      <c r="J12" t="n">
+        <v>11.9047619047619</v>
+      </c>
+      <c r="K12" t="n">
+        <v>9.048084077380953</v>
+      </c>
+      <c r="L12" t="n">
         <v>2</v>
       </c>
-      <c r="I12" t="n">
-        <v>0.5380144817073171</v>
-      </c>
-      <c r="J12" t="n">
-        <v>0.6097560975609756</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0.5738852896341464</v>
+      <c r="M12" t="n">
+        <v>11.9047619047619</v>
+      </c>
+      <c r="N12" t="n">
+        <v>10.50409226190476</v>
+      </c>
+      <c r="O12" t="n">
+        <v>2</v>
+      </c>
+      <c r="P12" t="n">
+        <v>8.720238095238095</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>5.063244047619047</v>
+      </c>
+      <c r="S12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Primary_v1_mm</t>
+        </is>
+      </c>
+      <c r="AD12" s="2" t="n">
+        <v>20.36142113095238</v>
       </c>
     </row>
     <row r="13">
@@ -1007,17 +1377,17 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>axial</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>7.15348007138608</v>
+        <v>2726.757369614512</v>
       </c>
       <c r="D13" t="n">
-        <v>14.8198112220299</v>
+        <v>289.3391714777265</v>
       </c>
       <c r="E13" t="n">
-        <v>11.78053873632012</v>
+        <v>230.0009943757738</v>
       </c>
       <c r="F13" t="n">
         <v>1.257990958965188</v>
@@ -1026,16 +1396,48 @@
         <v>0.4093001393888253</v>
       </c>
       <c r="H13" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I13" t="n">
-        <v>0.5236280487804879</v>
+        <v>5.0390625</v>
       </c>
       <c r="J13" t="n">
-        <v>0.5236280487804879</v>
+        <v>10.22321428571428</v>
       </c>
       <c r="K13" t="n">
-        <v>0.5236280487804879</v>
+        <v>8.504464285714285</v>
+      </c>
+      <c r="L13" t="n">
+        <v>1</v>
+      </c>
+      <c r="M13" t="n">
+        <v>10.22321428571428</v>
+      </c>
+      <c r="O13" t="n">
+        <v>3</v>
+      </c>
+      <c r="P13" t="n">
+        <v>9.574032738095237</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>9.181547619047619</v>
+      </c>
+      <c r="R13" t="n">
+        <v>5.0390625</v>
+      </c>
+      <c r="S13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Primary_v2_mm</t>
+        </is>
+      </c>
+      <c r="AD13" s="2" t="n">
+        <v>10.65383184523809</v>
       </c>
     </row>
     <row r="14">
@@ -1046,35 +1448,73 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>axial</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>7.466983938132064</v>
+        <v>2846.25850340136</v>
       </c>
       <c r="D14" t="n">
-        <v>13.76481526653941</v>
+        <v>268.7416313943409</v>
       </c>
       <c r="E14" t="n">
-        <v>11.42377244844669</v>
+        <v>223.0355573268164</v>
       </c>
       <c r="F14" t="n">
         <v>1.204927297760648</v>
       </c>
       <c r="G14" t="n">
-        <v>0.4952383941544979</v>
+        <v>0.4952383941544981</v>
       </c>
       <c r="H14" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I14" t="n">
-        <v>1.011051829268293</v>
+        <v>1.688988095238095</v>
       </c>
       <c r="J14" t="n">
-        <v>1.011051829268293</v>
+        <v>19.73958333333333</v>
       </c>
       <c r="K14" t="n">
-        <v>1.011051829268293</v>
+        <v>7.253844246031746</v>
+      </c>
+      <c r="L14" t="n">
+        <v>1</v>
+      </c>
+      <c r="M14" t="n">
+        <v>19.73958333333333</v>
+      </c>
+      <c r="O14" t="n">
+        <v>3</v>
+      </c>
+      <c r="P14" t="n">
+        <v>8.139880952380953</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>6.865699404761904</v>
+      </c>
+      <c r="R14" t="n">
+        <v>4.761904761904762</v>
+      </c>
+      <c r="S14" t="n">
+        <v>2</v>
+      </c>
+      <c r="T14" t="n">
+        <v>2.327008928571428</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1.688988095238095</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Secondary_count</t>
+        </is>
+      </c>
+      <c r="AD14" s="2" t="n">
+        <v>2.45</v>
       </c>
     </row>
     <row r="15">
@@ -1085,35 +1525,73 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>axial</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>7.549970255800119</v>
+        <v>2877.891156462585</v>
       </c>
       <c r="D15" t="n">
-        <v>13.36518658079752</v>
+        <v>260.9393570536659</v>
       </c>
       <c r="E15" t="n">
-        <v>11.2941698155752</v>
+        <v>220.5052202088492</v>
       </c>
       <c r="F15" t="n">
         <v>1.183370429083356</v>
       </c>
       <c r="G15" t="n">
-        <v>0.5311351612332996</v>
+        <v>0.5311351612332995</v>
       </c>
       <c r="H15" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I15" t="n">
-        <v>1.01219512195122</v>
+        <v>1.54389880952381</v>
       </c>
       <c r="J15" t="n">
-        <v>1.01219512195122</v>
+        <v>19.76190476190476</v>
       </c>
       <c r="K15" t="n">
-        <v>1.01219512195122</v>
+        <v>6.462363591269841</v>
+      </c>
+      <c r="L15" t="n">
+        <v>1</v>
+      </c>
+      <c r="M15" t="n">
+        <v>19.76190476190476</v>
+      </c>
+      <c r="O15" t="n">
+        <v>3</v>
+      </c>
+      <c r="P15" t="n">
+        <v>6.119791666666666</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>4.761904761904762</v>
+      </c>
+      <c r="R15" t="n">
+        <v>4.585193452380953</v>
+      </c>
+      <c r="S15" t="n">
+        <v>2</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2.001488095238095</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1.54389880952381</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Secondary_v1_mm</t>
+        </is>
+      </c>
+      <c r="AD15" s="2" t="n">
+        <v>6.957124255952381</v>
       </c>
     </row>
     <row r="16">
@@ -1124,17 +1602,17 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>axial</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>7.631171921475313</v>
+        <v>2908.843537414966</v>
       </c>
       <c r="D16" t="n">
-        <v>13.1035299533751</v>
+        <v>255.830822899228</v>
       </c>
       <c r="E16" t="n">
-        <v>11.19069078491955</v>
+        <v>218.4849153246198</v>
       </c>
       <c r="F16" t="n">
         <v>1.170931286121609</v>
@@ -1143,16 +1621,54 @@
         <v>0.5585016882641446</v>
       </c>
       <c r="H16" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I16" t="n">
-        <v>1.024390243902439</v>
+        <v>1.450892857142857</v>
       </c>
       <c r="J16" t="n">
-        <v>1.024390243902439</v>
+        <v>20</v>
       </c>
       <c r="K16" t="n">
-        <v>1.024390243902439</v>
+        <v>5.750558035714285</v>
+      </c>
+      <c r="L16" t="n">
+        <v>1</v>
+      </c>
+      <c r="M16" t="n">
+        <v>20</v>
+      </c>
+      <c r="O16" t="n">
+        <v>2</v>
+      </c>
+      <c r="P16" t="n">
+        <v>4.596354166666666</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>4.561011904761904</v>
+      </c>
+      <c r="S16" t="n">
+        <v>3</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2.371651785714286</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1.5234375</v>
+      </c>
+      <c r="V16" t="n">
+        <v>1.450892857142857</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Secondary_v2_mm</t>
+        </is>
+      </c>
+      <c r="AD16" s="2" t="n">
+        <v>6.148568802521008</v>
       </c>
     </row>
     <row r="17">
@@ -1163,17 +1679,17 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>axial</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>7.631171921475313</v>
+        <v>2908.843537414966</v>
       </c>
       <c r="D17" t="n">
-        <v>12.94535237114604</v>
+        <v>252.7425939128512</v>
       </c>
       <c r="E17" t="n">
-        <v>11.04680066864665</v>
+        <v>215.6756321021489</v>
       </c>
       <c r="F17" t="n">
         <v>1.171864393994898</v>
@@ -1182,16 +1698,54 @@
         <v>0.5722335924446625</v>
       </c>
       <c r="H17" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I17" t="n">
-        <v>0.9905678353658537</v>
+        <v>1.27046130952381</v>
       </c>
       <c r="J17" t="n">
-        <v>0.9905678353658537</v>
+        <v>19.33965773809524</v>
       </c>
       <c r="K17" t="n">
-        <v>0.9905678353658537</v>
+        <v>5.453249007936509</v>
+      </c>
+      <c r="L17" t="n">
+        <v>1</v>
+      </c>
+      <c r="M17" t="n">
+        <v>19.33965773809524</v>
+      </c>
+      <c r="O17" t="n">
+        <v>2</v>
+      </c>
+      <c r="P17" t="n">
+        <v>4.761904761904762</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>3.703497023809524</v>
+      </c>
+      <c r="S17" t="n">
+        <v>3</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2.001488095238095</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1.642485119047619</v>
+      </c>
+      <c r="V17" t="n">
+        <v>1.27046130952381</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Secondary_v3_mm</t>
+        </is>
+      </c>
+      <c r="AD17" s="2" t="n">
+        <v>4.932415674603175</v>
       </c>
     </row>
     <row r="18">
@@ -1202,17 +1756,17 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>axial</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>7.602914931588341</v>
+        <v>2898.072562358277</v>
       </c>
       <c r="D18" t="n">
-        <v>12.78472341269982</v>
+        <v>249.6065047241393</v>
       </c>
       <c r="E18" t="n">
-        <v>11.02414377142743</v>
+        <v>215.2332831564404</v>
       </c>
       <c r="F18" t="n">
         <v>1.159702166243104</v>
@@ -1221,16 +1775,54 @@
         <v>0.5845306945837129</v>
       </c>
       <c r="H18" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I18" t="n">
-        <v>0.951219512195122</v>
+        <v>1.233258928571429</v>
       </c>
       <c r="J18" t="n">
-        <v>0.951219512195122</v>
+        <v>18.57142857142857</v>
       </c>
       <c r="K18" t="n">
-        <v>0.951219512195122</v>
+        <v>5.143539186507936</v>
+      </c>
+      <c r="L18" t="n">
+        <v>1</v>
+      </c>
+      <c r="M18" t="n">
+        <v>18.57142857142857</v>
+      </c>
+      <c r="O18" t="n">
+        <v>2</v>
+      </c>
+      <c r="P18" t="n">
+        <v>4.285714285714286</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>3.333333333333333</v>
+      </c>
+      <c r="S18" t="n">
+        <v>3</v>
+      </c>
+      <c r="T18" t="n">
+        <v>1.720610119047619</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1.716889880952381</v>
+      </c>
+      <c r="V18" t="n">
+        <v>1.233258928571429</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Tertiary_count</t>
+        </is>
+      </c>
+      <c r="AD18" s="2" t="n">
+        <v>1.6</v>
       </c>
     </row>
     <row r="19">
@@ -1241,17 +1833,17 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>axial</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>7.53837001784652</v>
+        <v>2873.469387755102</v>
       </c>
       <c r="D19" t="n">
-        <v>12.72165549382931</v>
+        <v>248.3751786890484</v>
       </c>
       <c r="E19" t="n">
-        <v>10.93250089738427</v>
+        <v>213.4440651394072</v>
       </c>
       <c r="F19" t="n">
         <v>1.163654648944334</v>
@@ -1260,16 +1852,51 @@
         <v>0.585329016171437</v>
       </c>
       <c r="H19" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I19" t="n">
-        <v>0.990282012195122</v>
+        <v>1.277901785714286</v>
       </c>
       <c r="J19" t="n">
-        <v>0.990282012195122</v>
+        <v>19.33407738095238</v>
       </c>
       <c r="K19" t="n">
-        <v>0.990282012195122</v>
+        <v>5.239955357142857</v>
+      </c>
+      <c r="L19" t="n">
+        <v>1</v>
+      </c>
+      <c r="M19" t="n">
+        <v>19.33407738095238</v>
+      </c>
+      <c r="O19" t="n">
+        <v>1</v>
+      </c>
+      <c r="P19" t="n">
+        <v>5.022321428571428</v>
+      </c>
+      <c r="S19" t="n">
+        <v>4</v>
+      </c>
+      <c r="W19" t="n">
+        <v>1.277901785714286</v>
+      </c>
+      <c r="X19" t="n">
+        <v>2.380952380952381</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>1.770833333333333</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Tertiary_v1_mm</t>
+        </is>
+      </c>
+      <c r="AD19" s="2" t="n">
+        <v>1.64936755952381</v>
       </c>
     </row>
     <row r="20">
@@ -1280,17 +1907,17 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>axial</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>7.411957168352171</v>
+        <v>2825.283446712018</v>
       </c>
       <c r="D20" t="n">
-        <v>12.59797088692828</v>
+        <v>245.9603839828854</v>
       </c>
       <c r="E20" t="n">
-        <v>10.78024137020111</v>
+        <v>210.4713791324979</v>
       </c>
       <c r="F20" t="n">
         <v>1.168616773438094</v>
@@ -1299,16 +1926,51 @@
         <v>0.5868695333832172</v>
       </c>
       <c r="H20" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="I20" t="n">
-        <v>1.024390243902439</v>
+        <v>1.063988095238095</v>
       </c>
       <c r="J20" t="n">
-        <v>1.024390243902439</v>
+        <v>20</v>
       </c>
       <c r="K20" t="n">
-        <v>1.024390243902439</v>
+        <v>4.475446428571429</v>
+      </c>
+      <c r="L20" t="n">
+        <v>1</v>
+      </c>
+      <c r="M20" t="n">
+        <v>20</v>
+      </c>
+      <c r="O20" t="n">
+        <v>1</v>
+      </c>
+      <c r="P20" t="n">
+        <v>4.285714285714286</v>
+      </c>
+      <c r="S20" t="n">
+        <v>5</v>
+      </c>
+      <c r="W20" t="n">
+        <v>1.063988095238095</v>
+      </c>
+      <c r="X20" t="n">
+        <v>1.904761904761905</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>1.408482142857143</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Tertiary_v2_mm</t>
+        </is>
+      </c>
+      <c r="AD20" s="2" t="n">
+        <v>1.623139880952381</v>
       </c>
     </row>
     <row r="21">
@@ -1319,17 +1981,17 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>axial</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>7.330458060678168</v>
+        <v>2794.21768707483</v>
       </c>
       <c r="D21" t="n">
-        <v>12.73594293361757</v>
+        <v>248.6541239420573</v>
       </c>
       <c r="E21" t="n">
-        <v>10.73737892290441</v>
+        <v>209.6345408757527</v>
       </c>
       <c r="F21" t="n">
         <v>1.186131459554801</v>
@@ -1338,16 +2000,51 @@
         <v>0.5679090225740536</v>
       </c>
       <c r="H21" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="I21" t="n">
-        <v>1.111852134146341</v>
+        <v>1.1328125</v>
       </c>
       <c r="J21" t="n">
-        <v>1.111852134146341</v>
+        <v>21.70758928571428</v>
       </c>
       <c r="K21" t="n">
-        <v>1.111852134146341</v>
+        <v>4.774659863945579</v>
+      </c>
+      <c r="L21" t="n">
+        <v>1</v>
+      </c>
+      <c r="M21" t="n">
+        <v>21.70758928571428</v>
+      </c>
+      <c r="O21" t="n">
+        <v>1</v>
+      </c>
+      <c r="P21" t="n">
+        <v>4.577752976190476</v>
+      </c>
+      <c r="S21" t="n">
+        <v>5</v>
+      </c>
+      <c r="W21" t="n">
+        <v>1.1328125</v>
+      </c>
+      <c r="X21" t="n">
+        <v>1.904761904761905</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>1.427455357142857</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Tertiary_v3_mm</t>
+        </is>
+      </c>
+      <c r="AD21" s="2" t="n">
+        <v>1.318204365079365</v>
       </c>
     </row>
     <row r="22">
@@ -1357,7 +2054,15 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.02439024390243903</v>
+        <v>0.4761904761904762</v>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Tertiary_min_mm</t>
+        </is>
+      </c>
+      <c r="AD22" s="2" t="n">
+        <v>1.158234126984127</v>
       </c>
     </row>
     <row r="23">
@@ -1371,6 +2076,14 @@
           <t>mm</t>
         </is>
       </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Tertiary_max_mm</t>
+        </is>
+      </c>
+      <c r="AD23" s="2" t="n">
+        <v>2.063492063492064</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1380,6 +2093,54 @@
       </c>
       <c r="B24" t="n">
         <v>25</v>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Tertiary_mean_mm</t>
+        </is>
+      </c>
+      <c r="AD24" s="2" t="n">
+        <v>1.535590277777778</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>ScalebarMeasuredPixels:</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>42</v>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Unclassified_count</t>
+        </is>
+      </c>
+      <c r="AD25" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>ScalebarRealWorldLength:</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>ScalebarRealWorldUnit:</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>mm</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/measurements/28/Filled_2D_sections/axial/week28_axial_Batch_Allmarks.xlsx
+++ b/measurements/28/Filled_2D_sections/axial/week28_axial_Batch_Allmarks.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Analysis" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -137,6 +138,211 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>15</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4953000" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>15</col>
+      <colOff>0</colOff>
+      <row>23</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4953000" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="2" name="Image 2" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>15</col>
+      <colOff>0</colOff>
+      <row>45</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4953000" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="3" name="Image 3" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>15</col>
+      <colOff>0</colOff>
+      <row>67</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4953000" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="4" name="Image 4" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>24</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4953000" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="5" name="Image 5" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>24</col>
+      <colOff>0</colOff>
+      <row>23</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4953000" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="6" name="Image 6" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>24</col>
+      <colOff>0</colOff>
+      <row>45</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4953000" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="7" name="Image 7" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId7"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>35</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5905500" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="8" name="Image 8" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId8"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2146,4 +2352,1277 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K51"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Workbook Analysis</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Workbook</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>week28_axial_Batch_Allmarks.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Week</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Axis</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>axial</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Slice rows analyzed</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>When a sulcus class count exceeds 3, approximate raw sulcus values are reconstructed from count + min/max/mean for summary stats and boxplots.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Core Metric Summary</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>metric</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>mean</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>std</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>min</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>max</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>area</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>20</v>
+      </c>
+      <c r="C10" t="n">
+        <v>2848.894557823129</v>
+      </c>
+      <c r="D10" t="n">
+        <v>57.67474948052542</v>
+      </c>
+      <c r="E10" t="n">
+        <v>2726.757369614512</v>
+      </c>
+      <c r="F10" t="n">
+        <v>2930.725623582766</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>perimeter</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>20</v>
+      </c>
+      <c r="C11" t="n">
+        <v>278.3983155432201</v>
+      </c>
+      <c r="D11" t="n">
+        <v>26.08067176691548</v>
+      </c>
+      <c r="E11" t="n">
+        <v>245.9603839828854</v>
+      </c>
+      <c r="F11" t="n">
+        <v>322.46124176752</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>LGI</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>20</v>
+      </c>
+      <c r="C12" t="n">
+        <v>1.23246305775851</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0.09327257192793327</v>
+      </c>
+      <c r="E12" t="n">
+        <v>1.125611256387889</v>
+      </c>
+      <c r="F12" t="n">
+        <v>1.41793269967912</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Compactness</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>20</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0.4731195902887242</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0.08524276818012877</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.3473064105601356</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.5868695333832172</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Rounded Sulcus Counts Per Slice</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>File</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Sulci_count</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Primary_count</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Secondary_count</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Tertiary_count</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Unclassified_count</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Sulci_count_rounded</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Primary_count_rounded</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Secondary_count_rounded</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Tertiary_count_rounded</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Unclassified_count_rounded</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>band_axis2_s00_idx0112.png</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>5</v>
+      </c>
+      <c r="C17" t="n">
+        <v>1</v>
+      </c>
+      <c r="D17" t="n">
+        <v>3</v>
+      </c>
+      <c r="E17" t="n">
+        <v>1</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" t="n">
+        <v>5</v>
+      </c>
+      <c r="H17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I17" t="n">
+        <v>3</v>
+      </c>
+      <c r="J17" t="n">
+        <v>1</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>band_axis2_s01_idx0114.png</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>4</v>
+      </c>
+      <c r="C18" t="n">
+        <v>1</v>
+      </c>
+      <c r="D18" t="n">
+        <v>3</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" t="n">
+        <v>4</v>
+      </c>
+      <c r="H18" t="n">
+        <v>1</v>
+      </c>
+      <c r="I18" t="n">
+        <v>3</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>band_axis2_s02_idx0116.png</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>4</v>
+      </c>
+      <c r="C19" t="n">
+        <v>1</v>
+      </c>
+      <c r="D19" t="n">
+        <v>3</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" t="n">
+        <v>4</v>
+      </c>
+      <c r="H19" t="n">
+        <v>1</v>
+      </c>
+      <c r="I19" t="n">
+        <v>3</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>band_axis2_s03_idx0118.png</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>4</v>
+      </c>
+      <c r="C20" t="n">
+        <v>1</v>
+      </c>
+      <c r="D20" t="n">
+        <v>3</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" t="n">
+        <v>4</v>
+      </c>
+      <c r="H20" t="n">
+        <v>1</v>
+      </c>
+      <c r="I20" t="n">
+        <v>3</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>band_axis2_s04_idx0119.png</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>4</v>
+      </c>
+      <c r="C21" t="n">
+        <v>1</v>
+      </c>
+      <c r="D21" t="n">
+        <v>3</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" t="n">
+        <v>4</v>
+      </c>
+      <c r="H21" t="n">
+        <v>1</v>
+      </c>
+      <c r="I21" t="n">
+        <v>3</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>band_axis2_s05_idx0121.png</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>5</v>
+      </c>
+      <c r="C22" t="n">
+        <v>1</v>
+      </c>
+      <c r="D22" t="n">
+        <v>3</v>
+      </c>
+      <c r="E22" t="n">
+        <v>1</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" t="n">
+        <v>5</v>
+      </c>
+      <c r="H22" t="n">
+        <v>1</v>
+      </c>
+      <c r="I22" t="n">
+        <v>3</v>
+      </c>
+      <c r="J22" t="n">
+        <v>1</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>band_axis2_s06_idx0123.png</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>5</v>
+      </c>
+      <c r="C23" t="n">
+        <v>1</v>
+      </c>
+      <c r="D23" t="n">
+        <v>3</v>
+      </c>
+      <c r="E23" t="n">
+        <v>1</v>
+      </c>
+      <c r="F23" t="n">
+        <v>0</v>
+      </c>
+      <c r="G23" t="n">
+        <v>5</v>
+      </c>
+      <c r="H23" t="n">
+        <v>1</v>
+      </c>
+      <c r="I23" t="n">
+        <v>3</v>
+      </c>
+      <c r="J23" t="n">
+        <v>1</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>band_axis2_s07_idx0124.png</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>5</v>
+      </c>
+      <c r="C24" t="n">
+        <v>1</v>
+      </c>
+      <c r="D24" t="n">
+        <v>3</v>
+      </c>
+      <c r="E24" t="n">
+        <v>1</v>
+      </c>
+      <c r="F24" t="n">
+        <v>0</v>
+      </c>
+      <c r="G24" t="n">
+        <v>5</v>
+      </c>
+      <c r="H24" t="n">
+        <v>1</v>
+      </c>
+      <c r="I24" t="n">
+        <v>3</v>
+      </c>
+      <c r="J24" t="n">
+        <v>1</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>band_axis2_s08_idx0126.png</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>5</v>
+      </c>
+      <c r="C25" t="n">
+        <v>1</v>
+      </c>
+      <c r="D25" t="n">
+        <v>3</v>
+      </c>
+      <c r="E25" t="n">
+        <v>1</v>
+      </c>
+      <c r="F25" t="n">
+        <v>0</v>
+      </c>
+      <c r="G25" t="n">
+        <v>5</v>
+      </c>
+      <c r="H25" t="n">
+        <v>1</v>
+      </c>
+      <c r="I25" t="n">
+        <v>3</v>
+      </c>
+      <c r="J25" t="n">
+        <v>1</v>
+      </c>
+      <c r="K25" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>band_axis2_s09_idx0128.png</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>4</v>
+      </c>
+      <c r="C26" t="n">
+        <v>2</v>
+      </c>
+      <c r="D26" t="n">
+        <v>2</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0</v>
+      </c>
+      <c r="F26" t="n">
+        <v>0</v>
+      </c>
+      <c r="G26" t="n">
+        <v>4</v>
+      </c>
+      <c r="H26" t="n">
+        <v>2</v>
+      </c>
+      <c r="I26" t="n">
+        <v>2</v>
+      </c>
+      <c r="J26" t="n">
+        <v>0</v>
+      </c>
+      <c r="K26" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>band_axis2_s10_idx0129.png</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>4</v>
+      </c>
+      <c r="C27" t="n">
+        <v>2</v>
+      </c>
+      <c r="D27" t="n">
+        <v>2</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0</v>
+      </c>
+      <c r="F27" t="n">
+        <v>0</v>
+      </c>
+      <c r="G27" t="n">
+        <v>4</v>
+      </c>
+      <c r="H27" t="n">
+        <v>2</v>
+      </c>
+      <c r="I27" t="n">
+        <v>2</v>
+      </c>
+      <c r="J27" t="n">
+        <v>0</v>
+      </c>
+      <c r="K27" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>band_axis2_s11_idx0131.png</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>4</v>
+      </c>
+      <c r="C28" t="n">
+        <v>1</v>
+      </c>
+      <c r="D28" t="n">
+        <v>3</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0</v>
+      </c>
+      <c r="F28" t="n">
+        <v>0</v>
+      </c>
+      <c r="G28" t="n">
+        <v>4</v>
+      </c>
+      <c r="H28" t="n">
+        <v>1</v>
+      </c>
+      <c r="I28" t="n">
+        <v>3</v>
+      </c>
+      <c r="J28" t="n">
+        <v>0</v>
+      </c>
+      <c r="K28" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>band_axis2_s12_idx0133.png</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>6</v>
+      </c>
+      <c r="C29" t="n">
+        <v>1</v>
+      </c>
+      <c r="D29" t="n">
+        <v>3</v>
+      </c>
+      <c r="E29" t="n">
+        <v>2</v>
+      </c>
+      <c r="F29" t="n">
+        <v>0</v>
+      </c>
+      <c r="G29" t="n">
+        <v>6</v>
+      </c>
+      <c r="H29" t="n">
+        <v>1</v>
+      </c>
+      <c r="I29" t="n">
+        <v>3</v>
+      </c>
+      <c r="J29" t="n">
+        <v>2</v>
+      </c>
+      <c r="K29" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>band_axis2_s13_idx0134.png</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>6</v>
+      </c>
+      <c r="C30" t="n">
+        <v>1</v>
+      </c>
+      <c r="D30" t="n">
+        <v>3</v>
+      </c>
+      <c r="E30" t="n">
+        <v>2</v>
+      </c>
+      <c r="F30" t="n">
+        <v>0</v>
+      </c>
+      <c r="G30" t="n">
+        <v>6</v>
+      </c>
+      <c r="H30" t="n">
+        <v>1</v>
+      </c>
+      <c r="I30" t="n">
+        <v>3</v>
+      </c>
+      <c r="J30" t="n">
+        <v>2</v>
+      </c>
+      <c r="K30" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>band_axis2_s14_idx0136.png</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>6</v>
+      </c>
+      <c r="C31" t="n">
+        <v>1</v>
+      </c>
+      <c r="D31" t="n">
+        <v>2</v>
+      </c>
+      <c r="E31" t="n">
+        <v>3</v>
+      </c>
+      <c r="F31" t="n">
+        <v>0</v>
+      </c>
+      <c r="G31" t="n">
+        <v>6</v>
+      </c>
+      <c r="H31" t="n">
+        <v>1</v>
+      </c>
+      <c r="I31" t="n">
+        <v>2</v>
+      </c>
+      <c r="J31" t="n">
+        <v>3</v>
+      </c>
+      <c r="K31" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>band_axis2_s15_idx0138.png</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>6</v>
+      </c>
+      <c r="C32" t="n">
+        <v>1</v>
+      </c>
+      <c r="D32" t="n">
+        <v>2</v>
+      </c>
+      <c r="E32" t="n">
+        <v>3</v>
+      </c>
+      <c r="F32" t="n">
+        <v>0</v>
+      </c>
+      <c r="G32" t="n">
+        <v>6</v>
+      </c>
+      <c r="H32" t="n">
+        <v>1</v>
+      </c>
+      <c r="I32" t="n">
+        <v>2</v>
+      </c>
+      <c r="J32" t="n">
+        <v>3</v>
+      </c>
+      <c r="K32" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>band_axis2_s16_idx0139.png</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>6</v>
+      </c>
+      <c r="C33" t="n">
+        <v>1</v>
+      </c>
+      <c r="D33" t="n">
+        <v>2</v>
+      </c>
+      <c r="E33" t="n">
+        <v>3</v>
+      </c>
+      <c r="F33" t="n">
+        <v>0</v>
+      </c>
+      <c r="G33" t="n">
+        <v>6</v>
+      </c>
+      <c r="H33" t="n">
+        <v>1</v>
+      </c>
+      <c r="I33" t="n">
+        <v>2</v>
+      </c>
+      <c r="J33" t="n">
+        <v>3</v>
+      </c>
+      <c r="K33" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>band_axis2_s17_idx0141.png</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>6</v>
+      </c>
+      <c r="C34" t="n">
+        <v>1</v>
+      </c>
+      <c r="D34" t="n">
+        <v>1</v>
+      </c>
+      <c r="E34" t="n">
+        <v>4</v>
+      </c>
+      <c r="F34" t="n">
+        <v>0</v>
+      </c>
+      <c r="G34" t="n">
+        <v>6</v>
+      </c>
+      <c r="H34" t="n">
+        <v>1</v>
+      </c>
+      <c r="I34" t="n">
+        <v>1</v>
+      </c>
+      <c r="J34" t="n">
+        <v>4</v>
+      </c>
+      <c r="K34" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>band_axis2_s18_idx0143.png</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>7</v>
+      </c>
+      <c r="C35" t="n">
+        <v>1</v>
+      </c>
+      <c r="D35" t="n">
+        <v>1</v>
+      </c>
+      <c r="E35" t="n">
+        <v>5</v>
+      </c>
+      <c r="F35" t="n">
+        <v>0</v>
+      </c>
+      <c r="G35" t="n">
+        <v>7</v>
+      </c>
+      <c r="H35" t="n">
+        <v>1</v>
+      </c>
+      <c r="I35" t="n">
+        <v>1</v>
+      </c>
+      <c r="J35" t="n">
+        <v>5</v>
+      </c>
+      <c r="K35" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>band_axis2_s19_idx0144.png</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>7</v>
+      </c>
+      <c r="C36" t="n">
+        <v>1</v>
+      </c>
+      <c r="D36" t="n">
+        <v>1</v>
+      </c>
+      <c r="E36" t="n">
+        <v>5</v>
+      </c>
+      <c r="F36" t="n">
+        <v>0</v>
+      </c>
+      <c r="G36" t="n">
+        <v>7</v>
+      </c>
+      <c r="H36" t="n">
+        <v>1</v>
+      </c>
+      <c r="I36" t="n">
+        <v>1</v>
+      </c>
+      <c r="J36" t="n">
+        <v>5</v>
+      </c>
+      <c r="K36" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Rounded Sulcus Count Summary</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>metric</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>mean</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>std</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>min</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>max</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Sulci_count_rounded</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>20</v>
+      </c>
+      <c r="C40" t="n">
+        <v>5.15</v>
+      </c>
+      <c r="D40" t="n">
+        <v>1.039989878493258</v>
+      </c>
+      <c r="E40" t="n">
+        <v>4</v>
+      </c>
+      <c r="F40" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Primary_count_rounded</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>20</v>
+      </c>
+      <c r="C41" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="D41" t="n">
+        <v>0.3077935056255462</v>
+      </c>
+      <c r="E41" t="n">
+        <v>1</v>
+      </c>
+      <c r="F41" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Secondary_count_rounded</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>20</v>
+      </c>
+      <c r="C42" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="D42" t="n">
+        <v>0.7591546545162482</v>
+      </c>
+      <c r="E42" t="n">
+        <v>1</v>
+      </c>
+      <c r="F42" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Tertiary_count_rounded</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>20</v>
+      </c>
+      <c r="C43" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="D43" t="n">
+        <v>1.698296359978372</v>
+      </c>
+      <c r="E43" t="n">
+        <v>0</v>
+      </c>
+      <c r="F43" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Unclassified_count_rounded</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>20</v>
+      </c>
+      <c r="C44" t="n">
+        <v>0</v>
+      </c>
+      <c r="D44" t="n">
+        <v>0</v>
+      </c>
+      <c r="E44" t="n">
+        <v>0</v>
+      </c>
+      <c r="F44" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Sulcus Value Summary</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>metric</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>mean</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>std</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>min</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>max</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>primary_sulcus_values</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>22</v>
+      </c>
+      <c r="C48" t="n">
+        <v>19.47891301406926</v>
+      </c>
+      <c r="D48" t="n">
+        <v>6.149089617190806</v>
+      </c>
+      <c r="E48" t="n">
+        <v>10.22321428571428</v>
+      </c>
+      <c r="F48" t="n">
+        <v>30.16927083333333</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>secondary_sulcus_values</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>49</v>
+      </c>
+      <c r="C49" t="n">
+        <v>6.180758017492712</v>
+      </c>
+      <c r="D49" t="n">
+        <v>1.652011112016726</v>
+      </c>
+      <c r="E49" t="n">
+        <v>3.333333333333333</v>
+      </c>
+      <c r="F49" t="n">
+        <v>9.680059523809524</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>tertiary_sulcus_values</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>32</v>
+      </c>
+      <c r="C50" t="n">
+        <v>1.557094029017857</v>
+      </c>
+      <c r="D50" t="n">
+        <v>0.3698907913281564</v>
+      </c>
+      <c r="E50" t="n">
+        <v>1.063988095238095</v>
+      </c>
+      <c r="F50" t="n">
+        <v>2.380952380952381</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>unclassified_sulcus_values</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing r:id="rId1"/>
+</worksheet>
 </file>